--- a/BIP Report Setup Tmpl.xlsx
+++ b/BIP Report Setup Tmpl.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Crist\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8067c0248e73e406/Documents/WRK/GitHub/OracleSetupReports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3FB924-1F35-4B7C-A46E-F8D39E665A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{6D3FB924-1F35-4B7C-A46E-F8D39E665A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E19747C-F1CB-4D44-90C7-30811D6D2383}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{6723E2BA-4745-4283-9749-DCFF573B2A3B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Doc" sheetId="3" r:id="rId1"/>
     <sheet name="Parmeters" sheetId="4" r:id="rId2"/>
     <sheet name="Report" sheetId="1" r:id="rId3"/>
-    <sheet name="XDO_METADATA" sheetId="2" r:id="rId4"/>
+    <sheet name="XDO_METADATA" sheetId="2" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
@@ -58,9 +58,6 @@
     <t>www.linkedin.com/in/cristian-arakaki</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/cristian-arakaki/</t>
-  </si>
-  <si>
     <t>26C</t>
   </si>
   <si>
@@ -98,6 +95,9 @@
   </si>
   <si>
     <t>Report parameters</t>
+  </si>
+  <si>
+    <t>https://github.com/carakaki</t>
   </si>
 </sst>
 </file>
@@ -546,47 +546,47 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="A2" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="13">
         <v>46314</v>
@@ -594,7 +594,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" xr:uid="{8B346DE6-145E-4781-A39E-9DD661C006BF}"/>
+    <hyperlink ref="B9" r:id="rId1" display="https://www.linkedin.com/in/cristian-arakaki/" xr:uid="{8B346DE6-145E-4781-A39E-9DD661C006BF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -611,12 +611,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="14"/>
     </row>
@@ -635,7 +635,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1">
@@ -677,7 +677,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2">
